--- a/Config/Datas/facility_development.xlsx
+++ b/Config/Datas/facility_development.xlsx
@@ -2,41 +2,380 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_homestead_req" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="facility_development_definition" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="facility_development_level" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="town_facility_site" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="facility_renovation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="character_facility_supervisor" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -44,15 +383,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -405,7 +1034,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -416,7 +1044,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col width="37.375" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -517,8 +1148,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -528,30 +1159,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>logic_area_id</t>
+          <t>facility_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>display_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>display_name</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>max_level</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>max_level</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
@@ -575,7 +1201,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -584,11 +1210,6 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -625,11 +1246,6 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,124 +1255,135 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>逻辑区域id</t>
+          <t>设施cfgid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>设施id</t>
+          <t>显示名</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>显示名</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>最大等级</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>最大等级</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>图标</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>长老厅</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="D6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>商摊</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>传送门</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="D8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>village_01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>村政厅</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>酒馆</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>运输队营地</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -771,7 +1398,453 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="19.375" customWidth="1" min="2" max="2"/>
+    <col width="27.875" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>facility_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unlock_costs</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>daily_outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>设施cfgid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>目标等级</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>升级名</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>解锁条件</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>每日产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>初建</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>搭建基础议事厅</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>wood,20|stone,10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>gold,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>扩建</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>增加办事窗口</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>wood,40|stone,20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>gold,20|wood,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>完善</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>提升管理效率</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>wood,60|stone,30|gold,100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>gold,40|desire_shard,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>开张</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>启用商摊</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>wood,15|gold,50</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>gold,15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>扩容</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>扩大交易规模</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>wood,30|gold,120</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>gold,35|wood,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>修复</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>恢复传送功能</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>stone,25|gold,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>提升传送稳定性</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>stone,50|gold,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>接管</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>接管村政厅</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>wood,10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>wood,8|gold,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>整顿</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>整顿村务</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>wood,25|gold,60</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>wood,15|gold,15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,42 +1855,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>logic_area_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>map_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>slot</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>display_name</t>
+          <t>facility_cfg_id</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unlock_conds</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>unlock_costs</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>daily_outputs</t>
+          <t>sort_order</t>
         </is>
       </c>
     </row>
@@ -829,42 +1887,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(list#sep=;),CommonCheckCond</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(list#sep=|),TalentUnlockCost</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>(list#sep=|),TalentUnlockCost</t>
         </is>
       </c>
     </row>
@@ -899,21 +1942,6 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -923,347 +1951,865 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>逻辑区域id</t>
+          <t>信标id</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>设施id</t>
+          <t>地图id</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>目标等级</t>
+          <t>槽位名</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>升级名</t>
+          <t>设施cfgid</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>elder_hall</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>teleport_gate</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>facility_cfg_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>renovation_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>min_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>unlock_conds</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>learn_costs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>daily_outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),TalentUnlockCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>设施cfgid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>改造项id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>显示名</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>最低建筑等级</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>解锁条件</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>每日产出(控制城镇后结算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>学习消耗</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>每日产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>general_trade</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>通识贸易</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>偏重人类通识与稳定收入</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gold,8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>gold,12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>merchant_stall</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>scrap_focus</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>搜刮周转</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>快速消化搜刮物换钱</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>gold,15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>gold,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>council_basic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>基础议事</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>维持聚落秩序</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>初建</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>搭建基础议事厅</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>wood,20|stone,10</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>influence,2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>gold,32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>village_hall</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>patrol_support</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>巡防支援</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>为周边探索提供安定</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>stability,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gold_signboard</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>酒招挂牌</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>门外酒招吸引过客，提升金币收入</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>gold,12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ledger_counter</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>柜台账册</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>账房规范收银，稳定提升金币产出</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>gold,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>brew_cellar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>醇酿窖藏</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>窖藏烈酿抬升客单，大幅增加金币收入</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>gold,80</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>gold,32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>local_haul</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>短途驮运</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>服务聚落周边运输</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>gold,10</t>
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>can_assign_supervisor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>display_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>角色key</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>可派驻监工</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>头衔</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>elder_hall</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>长老</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>扩建</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>增加办事窗口</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>wood,40|stone,20</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>gold,20|wood,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>elder_hall</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>商摊主</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>home_vera</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>完善</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>提升管理效率</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>wood,60|stone,30|gold,100</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>gold,40|desire_shard,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>merchant_stall</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>侍从</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>开张</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>启用商摊</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>wood,15|gold,50</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>gold,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>merchant_stall</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>扩容</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>扩大交易规模</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>wood,30|gold,120</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>gold,35|wood,10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>teleport_gate</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>修复</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>恢复传送功能</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stone,25|gold,80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>homestead_01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>teleport_gate</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>强化</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>提升传送稳定性</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>stone,50|gold,200</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>village_01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>village_hall</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>接管</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>接管村政厅</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>wood,10</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>wood,8|gold,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>village_01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>village_hall</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>整顿</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>整顿村务</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>wood,25|gold,60</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>wood,15|gold,15</t>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>猎手</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/facility_development.xlsx
+++ b/Config/Datas/facility_development.xlsx
@@ -1279,111 +1279,134 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>市集</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>长老厅</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>商摊</t>
         </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>传送门</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>村政厅</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>酒馆</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>transport_camp</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>运输队营地</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>5</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1398,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="19.375" customWidth="1" min="2" max="2"/>
@@ -1573,263 +1596,363 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>市集 1级</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>提升市集经营能力</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>初建</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>搭建基础议事厅</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>wood,20|stone,10</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>gold,10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>扩建</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>增加办事窗口</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>wood,40|stone,20</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>gold,20|wood,5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>完善</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>提升管理效率</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>wood,60|stone,30|gold,100</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>gold,40|desire_shard,1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>开张</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>启用商摊</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>wood,15|gold,50</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>gold,15</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>扩容</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>扩大交易规模</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>wood,30|gold,120</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>gold,35|wood,10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>恢复传送功能</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>stone,25|gold,80</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>强化</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>提升传送稳定性</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>stone,50|gold,200</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>接管</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>接管村政厅</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>wood,10</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>wood,8|gold,5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>整顿</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>整顿村务</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>wood,25|gold,60</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>wood,15|gold,15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>市集 2级</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>提升市集经营能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>市集 3级</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>提升市集经营能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>市集 4级</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>提升市集经营能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>市集 5级</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>提升市集经营能力</t>
         </is>
       </c>
     </row>
@@ -1976,140 +2099,140 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>homestead_01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>homestead_01</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>transport_camp</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>transport_camp</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>homestead_01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>homestead_01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="B10" t="n">
         <v>5</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>homestead_01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>teleport_gate</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>village_01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2124,7 +2247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2301,11 @@
           <t>daily_outputs</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2230,6 +2358,11 @@
           <t>(list#sep=|),TalentUnlockCost</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),FacilityEffect</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2282,6 +2415,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2334,288 +2472,458 @@
           <t>每日产出</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>建筑和文明属性效果</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>general_trade</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>通识贸易</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>偏重人类通识与稳定收入</t>
         </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>gold,8</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>gold,12</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>merchant_stall</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>scrap_focus</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>搜刮周转</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>快速消化搜刮物换钱</t>
         </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>gold,15</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>gold,20</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>elder_hall</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>council_basic</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>基础议事</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>维持聚落秩序</t>
         </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>influence,2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>gold,32</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>village_hall</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>patrol_support</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>巡防支援</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>为周边探索提供安定</t>
         </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>stability,1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>gold_signboard</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>酒招挂牌</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>门外酒招吸引过客，提升金币收入</t>
         </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>gold,12</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>ledger_counter</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>柜台账册</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>账房规范收银，稳定提升金币产出</t>
         </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>gold,20</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>tavern</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>brew_cellar</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>醇酿窖藏</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>窖藏烈酿抬升客单，大幅增加金币收入</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>3</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>gold,80</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>gold,32</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>transport_camp</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>local_haul</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>短途驮运</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>服务聚落周边运输</t>
         </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>gold,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>market_shelf_1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>扩建货架 I</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>增加一个销售格。</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1,-,5,None,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>market_shelf_2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>扩建货架 II</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>再增加一个销售格。</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1,-,5,None,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>market_bidding</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>公开竞价</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>提高商品被买走的概率。</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1,-,3,None,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>market_appraisal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>鉴定柜台</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>提高售出商品的成交价格。</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1,-,4,None,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>market_guild_ledger</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>商会账房</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>增加销售格，并提高成交概率。</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1,-,5,None,1|1,-,3,None,1</t>
         </is>
       </c>
     </row>
@@ -2742,72 +3050,72 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="B6" t="b">
+      <c r="C6" t="b">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>长老</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="B7" t="b">
+      <c r="C7" t="b">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>商摊主</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>home_vera</t>
         </is>
       </c>
-      <c r="B8" t="b">
+      <c r="C8" t="b">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>侍从</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>carlisle</t>
         </is>
       </c>
-      <c r="B9" t="b">
+      <c r="C9" t="b">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>猎手</t>
         </is>

--- a/Config/Datas/facility_development.xlsx
+++ b/Config/Datas/facility_development.xlsx
@@ -1421,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="19.375" customWidth="1" min="2" max="2"/>
@@ -1953,6 +1953,156 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>提升市集经营能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>起建</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>搭建边境酒馆</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>wood,25|gold,80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>gold,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>扩建</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>增加情报与通识产出</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>wood,40|gold,150</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>gold,12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>完善</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>成为聚落情报枢纽</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>wood,60|gold,250</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>gold,20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>起建</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>搭建运输队营地</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>wood,30|stone,15</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>gold,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>transport_camp</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>扩建</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>扩大商队周转能力</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>wood,50|gold,120</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>gold,18</t>
         </is>
       </c>
     </row>
@@ -2510,11 +2660,6 @@
           <t>gold,8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>gold,12</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2586,9 +2731,9 @@
           <t>influence,2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>gold,32</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,-,None,7,2</t>
         </is>
       </c>
     </row>
@@ -2622,6 +2767,11 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>stability,1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,-,None,5,1</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/facility_development.xlsx
+++ b/Config/Datas/facility_development.xlsx
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2248,6 +2248,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="n">
         <v>1</v>
@@ -2361,29 +2362,6 @@
       </c>
       <c r="F10" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>village_01</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>village_hall</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>village_hall</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
